--- a/dashboards/grc_powerbi_data.xlsx
+++ b/dashboards/grc_powerbi_data.xlsx
@@ -166,12 +166,10 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CSFScores_tbl" displayName="CSFScores_tbl" ref="A1:C2" headerRowCount="1">
-  <autoFilter ref="A1:C2"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="function_name"/>
-    <tableColumn id="2" name="score"/>
-    <tableColumn id="3" name="rationale"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CSFScores_tbl" displayName="CSFScores_tbl" ref="A1:A2" headerRowCount="1">
+  <autoFilter ref="A1:A2"/>
+  <tableColumns count="1">
+    <tableColumn id="1" name="note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -188,29 +186,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="VendorAssessments_tbl" displayName="VendorAssessments_tbl" ref="A1:I2" headerRowCount="1">
-  <autoFilter ref="A1:I2"/>
-  <tableColumns count="9">
-    <tableColumn id="1" name="vendor_name"/>
-    <tableColumn id="2" name="service_type"/>
-    <tableColumn id="3" name="criticality"/>
-    <tableColumn id="4" name="risk_tier"/>
-    <tableColumn id="5" name="score"/>
-    <tableColumn id="6" name="gap_count"/>
-    <tableColumn id="7" name="critical_gaps"/>
-    <tableColumn id="8" name="assessor"/>
-    <tableColumn id="9" name="assessment_date"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="VendorAssessments_tbl" displayName="VendorAssessments_tbl" ref="A1:A2" headerRowCount="1">
+  <autoFilter ref="A1:A2"/>
+  <tableColumns count="1">
+    <tableColumn id="1" name="note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="VendorTierSummary_tbl" displayName="VendorTierSummary_tbl" ref="A1:B2" headerRowCount="1">
-  <autoFilter ref="A1:B2"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="risk_tier"/>
-    <tableColumn id="2" name="vendor_count"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="VendorTierSummary_tbl" displayName="VendorTierSummary_tbl" ref="A1:A2" headerRowCount="1">
+  <autoFilter ref="A1:A2"/>
+  <tableColumns count="1">
+    <tableColumn id="1" name="note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -604,22 +593,22 @@
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>4978406</v>
+        <v>4970939</v>
       </c>
       <c r="G2" t="n">
-        <v>2786241</v>
+        <v>3472874</v>
       </c>
       <c r="H2" t="n">
-        <v>11887270</v>
+        <v>11739442</v>
       </c>
       <c r="I2" t="n">
-        <v>17394445</v>
+        <v>15255780</v>
       </c>
       <c r="J2" t="n">
-        <v>75.047</v>
+        <v>76.06100000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>31.029</v>
+        <v>37.651</v>
       </c>
       <c r="L2" t="n">
         <v>350000</v>
@@ -657,22 +646,22 @@
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>5429943</v>
+        <v>5419843</v>
       </c>
       <c r="G3" t="n">
-        <v>2838461</v>
+        <v>3271517</v>
       </c>
       <c r="H3" t="n">
-        <v>13571782</v>
+        <v>13988206</v>
       </c>
       <c r="I3" t="n">
-        <v>20113814</v>
+        <v>18699724</v>
       </c>
       <c r="J3" t="n">
-        <v>67.65600000000001</v>
+        <v>68.03099999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>33.915</v>
+        <v>38.729</v>
       </c>
       <c r="L3" t="n">
         <v>500000</v>
@@ -710,22 +699,22 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2018282</v>
+        <v>2017033</v>
       </c>
       <c r="G4" t="n">
-        <v>868903</v>
+        <v>1040478</v>
       </c>
       <c r="H4" t="n">
-        <v>5040797</v>
+        <v>5272108</v>
       </c>
       <c r="I4" t="n">
-        <v>7836141</v>
+        <v>7409198</v>
       </c>
       <c r="J4" t="n">
-        <v>46.686</v>
+        <v>50.877</v>
       </c>
       <c r="K4" t="n">
-        <v>10.119</v>
+        <v>10.95</v>
       </c>
       <c r="L4" t="n">
         <v>280000</v>
@@ -763,22 +752,22 @@
         <v>1.5</v>
       </c>
       <c r="F5" t="n">
-        <v>2675921</v>
+        <v>2702990</v>
       </c>
       <c r="G5" t="n">
-        <v>916899</v>
+        <v>1008443</v>
       </c>
       <c r="H5" t="n">
-        <v>7074585</v>
+        <v>7626307</v>
       </c>
       <c r="I5" t="n">
-        <v>11008274</v>
+        <v>11020650</v>
       </c>
       <c r="J5" t="n">
-        <v>48.727</v>
+        <v>50.14100000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>15.492</v>
+        <v>18.199</v>
       </c>
       <c r="L5" t="n">
         <v>200000</v>
@@ -816,22 +805,22 @@
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>4419831</v>
+        <v>4464212</v>
       </c>
       <c r="G6" t="n">
-        <v>1931607</v>
+        <v>2955484</v>
       </c>
       <c r="H6" t="n">
-        <v>10295494</v>
+        <v>10241699</v>
       </c>
       <c r="I6" t="n">
-        <v>16303222</v>
+        <v>13914698</v>
       </c>
       <c r="J6" t="n">
-        <v>67.82599999999999</v>
+        <v>77.121</v>
       </c>
       <c r="K6" t="n">
-        <v>23.87</v>
+        <v>31.243</v>
       </c>
       <c r="L6" t="n">
         <v>180000</v>
@@ -894,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>82.7</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="3">
@@ -904,10 +893,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>450506</v>
+        <v>287699</v>
       </c>
       <c r="C3" t="n">
-        <v>81.34999999999999</v>
+        <v>82.20999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -917,10 +906,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>901013</v>
+        <v>575398</v>
       </c>
       <c r="C4" t="n">
-        <v>76.23999999999999</v>
+        <v>80.39</v>
       </c>
     </row>
     <row r="5">
@@ -930,10 +919,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1351519</v>
+        <v>863096</v>
       </c>
       <c r="C5" t="n">
-        <v>69.67</v>
+        <v>77.59</v>
       </c>
     </row>
     <row r="6">
@@ -943,10 +932,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1802026</v>
+        <v>1150795</v>
       </c>
       <c r="C6" t="n">
-        <v>62.92</v>
+        <v>74.31999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -956,10 +945,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2252532</v>
+        <v>1438494</v>
       </c>
       <c r="C7" t="n">
-        <v>56.82</v>
+        <v>71.18000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +958,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2703038</v>
+        <v>1726193</v>
       </c>
       <c r="C8" t="n">
-        <v>51.31</v>
+        <v>67.93000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -982,10 +971,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3153545</v>
+        <v>2013892</v>
       </c>
       <c r="C9" t="n">
-        <v>46.4</v>
+        <v>64.68000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -995,10 +984,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3604051</v>
+        <v>2301591</v>
       </c>
       <c r="C10" t="n">
-        <v>42.23</v>
+        <v>61.65</v>
       </c>
     </row>
     <row r="11">
@@ -1008,10 +997,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4054558</v>
+        <v>2589289</v>
       </c>
       <c r="C11" t="n">
-        <v>38.39</v>
+        <v>58.59</v>
       </c>
     </row>
     <row r="12">
@@ -1021,10 +1010,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4505064</v>
+        <v>2876988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.88</v>
+        <v>55.69</v>
       </c>
     </row>
     <row r="13">
@@ -1034,10 +1023,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4955571</v>
+        <v>3164687</v>
       </c>
       <c r="C13" t="n">
-        <v>31.82</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="14">
@@ -1047,10 +1036,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5406077</v>
+        <v>3452386</v>
       </c>
       <c r="C14" t="n">
-        <v>29.12</v>
+        <v>50.17</v>
       </c>
     </row>
     <row r="15">
@@ -1060,10 +1049,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5856583</v>
+        <v>3740085</v>
       </c>
       <c r="C15" t="n">
-        <v>26.7</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="16">
@@ -1073,10 +1062,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6307090</v>
+        <v>4027783</v>
       </c>
       <c r="C16" t="n">
-        <v>24.54</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="17">
@@ -1086,10 +1075,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6757596</v>
+        <v>4315482</v>
       </c>
       <c r="C17" t="n">
-        <v>22.68</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="18">
@@ -1099,10 +1088,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7208103</v>
+        <v>4603181</v>
       </c>
       <c r="C18" t="n">
-        <v>20.96</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="19">
@@ -1112,10 +1101,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7658609</v>
+        <v>4890880</v>
       </c>
       <c r="C19" t="n">
-        <v>19.4</v>
+        <v>38.43</v>
       </c>
     </row>
     <row r="20">
@@ -1125,10 +1114,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8109115</v>
+        <v>5178579</v>
       </c>
       <c r="C20" t="n">
-        <v>17.95</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="21">
@@ -1138,10 +1127,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8559622</v>
+        <v>5466278</v>
       </c>
       <c r="C21" t="n">
-        <v>16.68</v>
+        <v>34.53</v>
       </c>
     </row>
     <row r="22">
@@ -1151,10 +1140,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9010128</v>
+        <v>5753976</v>
       </c>
       <c r="C22" t="n">
-        <v>15.54</v>
+        <v>32.69</v>
       </c>
     </row>
     <row r="23">
@@ -1164,10 +1153,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9460635</v>
+        <v>6041675</v>
       </c>
       <c r="C23" t="n">
-        <v>14.47</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="24">
@@ -1177,10 +1166,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9911141</v>
+        <v>6329374</v>
       </c>
       <c r="C24" t="n">
-        <v>13.47</v>
+        <v>29.23</v>
       </c>
     </row>
     <row r="25">
@@ -1190,10 +1179,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10361648</v>
+        <v>6617073</v>
       </c>
       <c r="C25" t="n">
-        <v>12.56</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="26">
@@ -1203,10 +1192,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10812154</v>
+        <v>6904772</v>
       </c>
       <c r="C26" t="n">
-        <v>11.74</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="27">
@@ -1216,10 +1205,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11262660</v>
+        <v>7192470</v>
       </c>
       <c r="C27" t="n">
-        <v>11.02</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="28">
@@ -1229,10 +1218,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11713167</v>
+        <v>7480169</v>
       </c>
       <c r="C28" t="n">
-        <v>10.33</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="29">
@@ -1242,10 +1231,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12163673</v>
+        <v>7767868</v>
       </c>
       <c r="C29" t="n">
-        <v>9.710000000000001</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="30">
@@ -1255,10 +1244,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>12614180</v>
+        <v>8055567</v>
       </c>
       <c r="C30" t="n">
-        <v>9.119999999999999</v>
+        <v>20.92</v>
       </c>
     </row>
     <row r="31">
@@ -1268,10 +1257,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>13064686</v>
+        <v>8343266</v>
       </c>
       <c r="C31" t="n">
-        <v>8.56</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="32">
@@ -1281,10 +1270,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13515192</v>
+        <v>8630965</v>
       </c>
       <c r="C32" t="n">
-        <v>8.050000000000001</v>
+        <v>18.66</v>
       </c>
     </row>
     <row r="33">
@@ -1294,10 +1283,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>13965699</v>
+        <v>8918663</v>
       </c>
       <c r="C33" t="n">
-        <v>7.63</v>
+        <v>17.61</v>
       </c>
     </row>
     <row r="34">
@@ -1307,10 +1296,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>14416205</v>
+        <v>9206362</v>
       </c>
       <c r="C34" t="n">
-        <v>7.21</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="35">
@@ -1320,10 +1309,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>14866712</v>
+        <v>9494061</v>
       </c>
       <c r="C35" t="n">
-        <v>6.84</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="36">
@@ -1333,10 +1322,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15317218</v>
+        <v>9781760</v>
       </c>
       <c r="C36" t="n">
-        <v>6.46</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="37">
@@ -1346,10 +1335,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15767724</v>
+        <v>10069459</v>
       </c>
       <c r="C37" t="n">
-        <v>6.12</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="38">
@@ -1359,10 +1348,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16218231</v>
+        <v>10357157</v>
       </c>
       <c r="C38" t="n">
-        <v>5.8</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="39">
@@ -1372,10 +1361,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16668737</v>
+        <v>10644856</v>
       </c>
       <c r="C39" t="n">
-        <v>5.48</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="40">
@@ -1385,10 +1374,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17119244</v>
+        <v>10932555</v>
       </c>
       <c r="C40" t="n">
-        <v>5.19</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="41">
@@ -1398,10 +1387,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17569750</v>
+        <v>11220254</v>
       </c>
       <c r="C41" t="n">
-        <v>4.94</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="42">
@@ -1411,10 +1400,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18020257</v>
+        <v>11507953</v>
       </c>
       <c r="C42" t="n">
-        <v>4.68</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="43">
@@ -1424,10 +1413,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18470763</v>
+        <v>11795652</v>
       </c>
       <c r="C43" t="n">
-        <v>4.47</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="44">
@@ -1437,10 +1426,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18921269</v>
+        <v>12083350</v>
       </c>
       <c r="C44" t="n">
-        <v>4.24</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="45">
@@ -1450,10 +1439,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19371776</v>
+        <v>12371049</v>
       </c>
       <c r="C45" t="n">
-        <v>4.05</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="46">
@@ -1463,10 +1452,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19822282</v>
+        <v>12658748</v>
       </c>
       <c r="C46" t="n">
-        <v>3.86</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="47">
@@ -1476,10 +1465,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>20272789</v>
+        <v>12946447</v>
       </c>
       <c r="C47" t="n">
-        <v>3.69</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="48">
@@ -1489,10 +1478,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>20723295</v>
+        <v>13234146</v>
       </c>
       <c r="C48" t="n">
-        <v>3.54</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="49">
@@ -1502,10 +1491,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>21173801</v>
+        <v>13521844</v>
       </c>
       <c r="C49" t="n">
-        <v>3.36</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="50">
@@ -1515,10 +1504,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>21624308</v>
+        <v>13809543</v>
       </c>
       <c r="C50" t="n">
-        <v>3.19</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="51">
@@ -1528,10 +1517,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>22074814</v>
+        <v>14097242</v>
       </c>
       <c r="C51" t="n">
-        <v>3.08</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="52">
@@ -1541,10 +1530,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>22525321</v>
+        <v>14384941</v>
       </c>
       <c r="C52" t="n">
-        <v>2.94</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="53">
@@ -1554,10 +1543,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22975827</v>
+        <v>14672640</v>
       </c>
       <c r="C53" t="n">
-        <v>2.81</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="54">
@@ -1567,10 +1556,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>23426333</v>
+        <v>14960339</v>
       </c>
       <c r="C54" t="n">
-        <v>2.68</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="55">
@@ -1580,10 +1569,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>23876840</v>
+        <v>15248037</v>
       </c>
       <c r="C55" t="n">
-        <v>2.57</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="56">
@@ -1593,10 +1582,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>24327346</v>
+        <v>15535736</v>
       </c>
       <c r="C56" t="n">
-        <v>2.47</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="57">
@@ -1606,10 +1595,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24777853</v>
+        <v>15823435</v>
       </c>
       <c r="C57" t="n">
-        <v>2.34</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="58">
@@ -1619,10 +1608,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25228359</v>
+        <v>16111134</v>
       </c>
       <c r="C58" t="n">
-        <v>2.24</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="59">
@@ -1632,10 +1621,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25678866</v>
+        <v>16398833</v>
       </c>
       <c r="C59" t="n">
-        <v>2.14</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="60">
@@ -1645,10 +1634,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>26129372</v>
+        <v>16686531</v>
       </c>
       <c r="C60" t="n">
-        <v>2.05</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="61">
@@ -1658,10 +1647,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>26579878</v>
+        <v>16974230</v>
       </c>
       <c r="C61" t="n">
-        <v>1.99</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="62">
@@ -1671,10 +1660,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>27030385</v>
+        <v>17261929</v>
       </c>
       <c r="C62" t="n">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="63">
@@ -1684,10 +1673,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>27480891</v>
+        <v>17549628</v>
       </c>
       <c r="C63" t="n">
-        <v>1.84</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="64">
@@ -1697,10 +1686,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>27931398</v>
+        <v>17837327</v>
       </c>
       <c r="C64" t="n">
-        <v>1.76</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="65">
@@ -1710,10 +1699,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>28381904</v>
+        <v>18125026</v>
       </c>
       <c r="C65" t="n">
-        <v>1.7</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="66">
@@ -1723,10 +1712,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>28832410</v>
+        <v>18412724</v>
       </c>
       <c r="C66" t="n">
-        <v>1.64</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="67">
@@ -1736,10 +1725,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>29282917</v>
+        <v>18700423</v>
       </c>
       <c r="C67" t="n">
-        <v>1.56</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="68">
@@ -1749,10 +1738,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>29733423</v>
+        <v>18988122</v>
       </c>
       <c r="C68" t="n">
-        <v>1.52</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="69">
@@ -1762,10 +1751,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30183930</v>
+        <v>19275821</v>
       </c>
       <c r="C69" t="n">
-        <v>1.47</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="70">
@@ -1775,10 +1764,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>30634436</v>
+        <v>19563520</v>
       </c>
       <c r="C70" t="n">
-        <v>1.42</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="71">
@@ -1788,10 +1777,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>31084943</v>
+        <v>19851218</v>
       </c>
       <c r="C71" t="n">
-        <v>1.37</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="72">
@@ -1801,10 +1790,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>31535449</v>
+        <v>20138917</v>
       </c>
       <c r="C72" t="n">
-        <v>1.32</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="73">
@@ -1814,10 +1803,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>31985955</v>
+        <v>20426616</v>
       </c>
       <c r="C73" t="n">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="74">
@@ -1827,10 +1816,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>32436462</v>
+        <v>20714315</v>
       </c>
       <c r="C74" t="n">
-        <v>1.23</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="75">
@@ -1840,10 +1829,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>32886968</v>
+        <v>21002014</v>
       </c>
       <c r="C75" t="n">
-        <v>1.18</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="76">
@@ -1853,10 +1842,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>33337475</v>
+        <v>21289713</v>
       </c>
       <c r="C76" t="n">
-        <v>1.13</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="77">
@@ -1866,10 +1855,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>33787981</v>
+        <v>21577411</v>
       </c>
       <c r="C77" t="n">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="78">
@@ -1879,10 +1868,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>34238487</v>
+        <v>21865110</v>
       </c>
       <c r="C78" t="n">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="79">
@@ -1892,10 +1881,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>34688994</v>
+        <v>22152809</v>
       </c>
       <c r="C79" t="n">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="80">
@@ -1905,10 +1894,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>35139500</v>
+        <v>22440508</v>
       </c>
       <c r="C80" t="n">
-        <v>0.99</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="81">
@@ -1918,10 +1907,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35590007</v>
+        <v>22728207</v>
       </c>
       <c r="C81" t="n">
-        <v>0.95</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="82">
@@ -1931,10 +1920,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>36040513</v>
+        <v>23015905</v>
       </c>
       <c r="C82" t="n">
-        <v>0.91</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="83">
@@ -1944,10 +1933,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>36491019</v>
+        <v>23303604</v>
       </c>
       <c r="C83" t="n">
-        <v>0.88</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="84">
@@ -1957,10 +1946,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>36941526</v>
+        <v>23591303</v>
       </c>
       <c r="C84" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="85">
@@ -1970,10 +1959,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>37392032</v>
+        <v>23879002</v>
       </c>
       <c r="C85" t="n">
-        <v>0.82</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="86">
@@ -1983,10 +1972,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>37842539</v>
+        <v>24166701</v>
       </c>
       <c r="C86" t="n">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="87">
@@ -1996,10 +1985,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>38293045</v>
+        <v>24454400</v>
       </c>
       <c r="C87" t="n">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="88">
@@ -2009,10 +1998,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>38743552</v>
+        <v>24742098</v>
       </c>
       <c r="C88" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="89">
@@ -2022,10 +2011,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>39194058</v>
+        <v>25029797</v>
       </c>
       <c r="C89" t="n">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="90">
@@ -2035,10 +2024,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>39644564</v>
+        <v>25317496</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="91">
@@ -2048,10 +2037,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>40095071</v>
+        <v>25605195</v>
       </c>
       <c r="C91" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="92">
@@ -2061,10 +2050,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>40545577</v>
+        <v>25892894</v>
       </c>
       <c r="C92" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="93">
@@ -2074,10 +2063,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>40996084</v>
+        <v>26180592</v>
       </c>
       <c r="C93" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="94">
@@ -2087,10 +2076,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>41446590</v>
+        <v>26468291</v>
       </c>
       <c r="C94" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="95">
@@ -2100,10 +2089,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>41897096</v>
+        <v>26755990</v>
       </c>
       <c r="C95" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="96">
@@ -2113,10 +2102,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>42347603</v>
+        <v>27043689</v>
       </c>
       <c r="C96" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="97">
@@ -2126,10 +2115,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>42798109</v>
+        <v>27331388</v>
       </c>
       <c r="C97" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="98">
@@ -2139,10 +2128,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>43248616</v>
+        <v>27619087</v>
       </c>
       <c r="C98" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="99">
@@ -2152,10 +2141,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>43699122</v>
+        <v>27906785</v>
       </c>
       <c r="C99" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="100">
@@ -2165,7 +2154,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>44149628</v>
+        <v>28194484</v>
       </c>
       <c r="C100" t="n">
         <v>0.52</v>
@@ -2178,7 +2167,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>44600135</v>
+        <v>28482183</v>
       </c>
       <c r="C101" t="n">
         <v>0.5</v>
@@ -2194,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>71.52</v>
+        <v>71.05</v>
       </c>
     </row>
     <row r="103">
@@ -2204,10 +2193,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>513490</v>
+        <v>363495</v>
       </c>
       <c r="C103" t="n">
-        <v>70.95</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -2217,10 +2206,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1026980</v>
+        <v>726990</v>
       </c>
       <c r="C104" t="n">
-        <v>67.92</v>
+        <v>69.67</v>
       </c>
     </row>
     <row r="105">
@@ -2230,10 +2219,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1540469</v>
+        <v>1090485</v>
       </c>
       <c r="C105" t="n">
-        <v>63.15</v>
+        <v>67.43000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -2243,10 +2232,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2053959</v>
+        <v>1453980</v>
       </c>
       <c r="C106" t="n">
-        <v>57.93</v>
+        <v>64.61</v>
       </c>
     </row>
     <row r="107">
@@ -2256,10 +2245,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2567449</v>
+        <v>1817475</v>
       </c>
       <c r="C107" t="n">
-        <v>52.87</v>
+        <v>61.51</v>
       </c>
     </row>
     <row r="108">
@@ -2269,10 +2258,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3080939</v>
+        <v>2180970</v>
       </c>
       <c r="C108" t="n">
-        <v>48.22</v>
+        <v>58.52</v>
       </c>
     </row>
     <row r="109">
@@ -2282,10 +2271,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3594429</v>
+        <v>2544465</v>
       </c>
       <c r="C109" t="n">
-        <v>43.93</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="110">
@@ -2295,10 +2284,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>4107919</v>
+        <v>2907960</v>
       </c>
       <c r="C110" t="n">
-        <v>40.04</v>
+        <v>52.73</v>
       </c>
     </row>
     <row r="111">
@@ -2308,10 +2297,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>4621408</v>
+        <v>3271455</v>
       </c>
       <c r="C111" t="n">
-        <v>36.58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="112">
@@ -2321,10 +2310,10 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>5134898</v>
+        <v>3634950</v>
       </c>
       <c r="C112" t="n">
-        <v>33.38</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="113">
@@ -2334,10 +2323,10 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>5648388</v>
+        <v>3998445</v>
       </c>
       <c r="C113" t="n">
-        <v>30.64</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="114">
@@ -2347,10 +2336,10 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>6161878</v>
+        <v>4361940</v>
       </c>
       <c r="C114" t="n">
-        <v>28.07</v>
+        <v>42.48</v>
       </c>
     </row>
     <row r="115">
@@ -2360,10 +2349,10 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>6675368</v>
+        <v>4725435</v>
       </c>
       <c r="C115" t="n">
-        <v>25.92</v>
+        <v>40.31</v>
       </c>
     </row>
     <row r="116">
@@ -2373,10 +2362,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>7188858</v>
+        <v>5088930</v>
       </c>
       <c r="C116" t="n">
-        <v>23.97</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="117">
@@ -2386,10 +2375,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>7702347</v>
+        <v>5452425</v>
       </c>
       <c r="C117" t="n">
-        <v>22.12</v>
+        <v>36.24</v>
       </c>
     </row>
     <row r="118">
@@ -2399,10 +2388,10 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>8215837</v>
+        <v>5815920</v>
       </c>
       <c r="C118" t="n">
-        <v>20.49</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="119">
@@ -2412,10 +2401,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>8729327</v>
+        <v>6179415</v>
       </c>
       <c r="C119" t="n">
-        <v>19.05</v>
+        <v>32.49</v>
       </c>
     </row>
     <row r="120">
@@ -2425,10 +2414,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>9242817</v>
+        <v>6542910</v>
       </c>
       <c r="C120" t="n">
-        <v>17.68</v>
+        <v>30.73</v>
       </c>
     </row>
     <row r="121">
@@ -2438,10 +2427,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>9756307</v>
+        <v>6906405</v>
       </c>
       <c r="C121" t="n">
-        <v>16.44</v>
+        <v>29.04</v>
       </c>
     </row>
     <row r="122">
@@ -2451,10 +2440,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>10269797</v>
+        <v>7269900</v>
       </c>
       <c r="C122" t="n">
-        <v>15.33</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="123">
@@ -2464,10 +2453,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>10783286</v>
+        <v>7633395</v>
       </c>
       <c r="C123" t="n">
-        <v>14.28</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="124">
@@ -2477,10 +2466,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>11296776</v>
+        <v>7996890</v>
       </c>
       <c r="C124" t="n">
-        <v>13.33</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="125">
@@ -2490,10 +2479,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>11810266</v>
+        <v>8360384</v>
       </c>
       <c r="C125" t="n">
-        <v>12.53</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="126">
@@ -2503,10 +2492,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>12323756</v>
+        <v>8723879</v>
       </c>
       <c r="C126" t="n">
-        <v>11.76</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="127">
@@ -2516,10 +2505,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>12837246</v>
+        <v>9087374</v>
       </c>
       <c r="C127" t="n">
-        <v>11.03</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="128">
@@ -2529,10 +2518,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>13350736</v>
+        <v>9450869</v>
       </c>
       <c r="C128" t="n">
-        <v>10.35</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="129">
@@ -2542,10 +2531,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>13864225</v>
+        <v>9814364</v>
       </c>
       <c r="C129" t="n">
-        <v>9.74</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="130">
@@ -2555,10 +2544,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>14377715</v>
+        <v>10177859</v>
       </c>
       <c r="C130" t="n">
-        <v>9.17</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="131">
@@ -2568,10 +2557,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>14891205</v>
+        <v>10541354</v>
       </c>
       <c r="C131" t="n">
-        <v>8.609999999999999</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="132">
@@ -2581,10 +2570,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>15404695</v>
+        <v>10904849</v>
       </c>
       <c r="C132" t="n">
-        <v>8.08</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="133">
@@ -2594,10 +2583,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>15918185</v>
+        <v>11268344</v>
       </c>
       <c r="C133" t="n">
-        <v>7.64</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="134">
@@ -2607,10 +2596,10 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>16431675</v>
+        <v>11631839</v>
       </c>
       <c r="C134" t="n">
-        <v>7.24</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="135">
@@ -2620,10 +2609,10 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>16945164</v>
+        <v>11995334</v>
       </c>
       <c r="C135" t="n">
-        <v>6.83</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="136">
@@ -2633,10 +2622,10 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>17458654</v>
+        <v>12358829</v>
       </c>
       <c r="C136" t="n">
-        <v>6.49</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="137">
@@ -2646,10 +2635,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>17972144</v>
+        <v>12722324</v>
       </c>
       <c r="C137" t="n">
-        <v>6.12</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="138">
@@ -2659,10 +2648,10 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>18485634</v>
+        <v>13085819</v>
       </c>
       <c r="C138" t="n">
-        <v>5.8</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="139">
@@ -2672,10 +2661,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>18999124</v>
+        <v>13449314</v>
       </c>
       <c r="C139" t="n">
-        <v>5.55</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="140">
@@ -2685,10 +2674,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>19512614</v>
+        <v>13812809</v>
       </c>
       <c r="C140" t="n">
-        <v>5.24</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="141">
@@ -2698,10 +2687,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>20026103</v>
+        <v>14176304</v>
       </c>
       <c r="C141" t="n">
-        <v>4.98</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="142">
@@ -2711,10 +2700,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>20539593</v>
+        <v>14539799</v>
       </c>
       <c r="C142" t="n">
-        <v>4.72</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="143">
@@ -2724,10 +2713,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>21053083</v>
+        <v>14903294</v>
       </c>
       <c r="C143" t="n">
-        <v>4.48</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="144">
@@ -2737,10 +2726,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>21566573</v>
+        <v>15266789</v>
       </c>
       <c r="C144" t="n">
-        <v>4.25</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="145">
@@ -2750,10 +2739,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>22080063</v>
+        <v>15630284</v>
       </c>
       <c r="C145" t="n">
-        <v>4.05</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="146">
@@ -2763,10 +2752,10 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>22593553</v>
+        <v>15993779</v>
       </c>
       <c r="C146" t="n">
-        <v>3.87</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="147">
@@ -2776,10 +2765,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>23107042</v>
+        <v>16357274</v>
       </c>
       <c r="C147" t="n">
-        <v>3.71</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="148">
@@ -2789,10 +2778,10 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>23620532</v>
+        <v>16720769</v>
       </c>
       <c r="C148" t="n">
-        <v>3.53</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="149">
@@ -2802,10 +2791,10 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>24134022</v>
+        <v>17084264</v>
       </c>
       <c r="C149" t="n">
-        <v>3.37</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="150">
@@ -2815,10 +2804,10 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>24647512</v>
+        <v>17447759</v>
       </c>
       <c r="C150" t="n">
-        <v>3.23</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="151">
@@ -2828,10 +2817,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>25161002</v>
+        <v>17811254</v>
       </c>
       <c r="C151" t="n">
-        <v>3.11</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="152">
@@ -2841,10 +2830,10 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>25674492</v>
+        <v>18174749</v>
       </c>
       <c r="C152" t="n">
-        <v>2.98</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="153">
@@ -2854,10 +2843,10 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>26187981</v>
+        <v>18538244</v>
       </c>
       <c r="C153" t="n">
-        <v>2.84</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="154">
@@ -2867,10 +2856,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>26701471</v>
+        <v>18901739</v>
       </c>
       <c r="C154" t="n">
-        <v>2.73</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="155">
@@ -2880,10 +2869,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>27214961</v>
+        <v>19265234</v>
       </c>
       <c r="C155" t="n">
-        <v>2.63</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="156">
@@ -2893,10 +2882,10 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>27728451</v>
+        <v>19628729</v>
       </c>
       <c r="C156" t="n">
-        <v>2.5</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="157">
@@ -2906,10 +2895,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>28241941</v>
+        <v>19992224</v>
       </c>
       <c r="C157" t="n">
-        <v>2.39</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="158">
@@ -2919,10 +2908,10 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>28755431</v>
+        <v>20355719</v>
       </c>
       <c r="C158" t="n">
-        <v>2.28</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="159">
@@ -2932,10 +2921,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>29268920</v>
+        <v>20719214</v>
       </c>
       <c r="C159" t="n">
-        <v>2.19</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="160">
@@ -2945,10 +2934,10 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>29782410</v>
+        <v>21082709</v>
       </c>
       <c r="C160" t="n">
-        <v>2.1</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="161">
@@ -2958,10 +2947,10 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>30295900</v>
+        <v>21446204</v>
       </c>
       <c r="C161" t="n">
-        <v>2.01</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="162">
@@ -2971,10 +2960,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>30809390</v>
+        <v>21809699</v>
       </c>
       <c r="C162" t="n">
-        <v>1.93</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="163">
@@ -2984,10 +2973,10 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>31322880</v>
+        <v>22173194</v>
       </c>
       <c r="C163" t="n">
-        <v>1.84</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="164">
@@ -2997,10 +2986,10 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>31836370</v>
+        <v>22536689</v>
       </c>
       <c r="C164" t="n">
-        <v>1.77</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="165">
@@ -3010,10 +2999,10 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>32349859</v>
+        <v>22900184</v>
       </c>
       <c r="C165" t="n">
-        <v>1.7</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="166">
@@ -3023,10 +3012,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>32863349</v>
+        <v>23263679</v>
       </c>
       <c r="C166" t="n">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="167">
@@ -3036,10 +3025,10 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>33376839</v>
+        <v>23627174</v>
       </c>
       <c r="C167" t="n">
-        <v>1.57</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="168">
@@ -3049,10 +3038,10 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>33890329</v>
+        <v>23990669</v>
       </c>
       <c r="C168" t="n">
-        <v>1.51</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="169">
@@ -3062,10 +3051,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>34403819</v>
+        <v>24354164</v>
       </c>
       <c r="C169" t="n">
-        <v>1.44</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="170">
@@ -3075,10 +3064,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>34917309</v>
+        <v>24717659</v>
       </c>
       <c r="C170" t="n">
-        <v>1.39</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="171">
@@ -3088,10 +3077,10 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>35430798</v>
+        <v>25081153</v>
       </c>
       <c r="C171" t="n">
-        <v>1.34</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="172">
@@ -3101,10 +3090,10 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>35944288</v>
+        <v>25444648</v>
       </c>
       <c r="C172" t="n">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="173">
@@ -3114,10 +3103,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>36457778</v>
+        <v>25808143</v>
       </c>
       <c r="C173" t="n">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="174">
@@ -3127,10 +3116,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>36971268</v>
+        <v>26171638</v>
       </c>
       <c r="C174" t="n">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="175">
@@ -3140,10 +3129,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>37484758</v>
+        <v>26535133</v>
       </c>
       <c r="C175" t="n">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="176">
@@ -3153,10 +3142,10 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>37998248</v>
+        <v>26898628</v>
       </c>
       <c r="C176" t="n">
-        <v>1.1</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="177">
@@ -3166,10 +3155,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>38511737</v>
+        <v>27262123</v>
       </c>
       <c r="C177" t="n">
-        <v>1.06</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="178">
@@ -3179,10 +3168,10 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>39025227</v>
+        <v>27625618</v>
       </c>
       <c r="C178" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="179">
@@ -3192,10 +3181,10 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>39538717</v>
+        <v>27989113</v>
       </c>
       <c r="C179" t="n">
-        <v>0.99</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="180">
@@ -3205,10 +3194,10 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>40052207</v>
+        <v>28352608</v>
       </c>
       <c r="C180" t="n">
-        <v>0.95</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="181">
@@ -3218,10 +3207,10 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>40565697</v>
+        <v>28716103</v>
       </c>
       <c r="C181" t="n">
-        <v>0.92</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="182">
@@ -3231,10 +3220,10 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>41079187</v>
+        <v>29079598</v>
       </c>
       <c r="C182" t="n">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="183">
@@ -3244,10 +3233,10 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>41592676</v>
+        <v>29443093</v>
       </c>
       <c r="C183" t="n">
-        <v>0.85</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="184">
@@ -3257,10 +3246,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>42106166</v>
+        <v>29806588</v>
       </c>
       <c r="C184" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="185">
@@ -3270,10 +3259,10 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>42619656</v>
+        <v>30170083</v>
       </c>
       <c r="C185" t="n">
-        <v>0.79</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="186">
@@ -3283,10 +3272,10 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>43133146</v>
+        <v>30533578</v>
       </c>
       <c r="C186" t="n">
-        <v>0.76</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="187">
@@ -3296,10 +3285,10 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>43646636</v>
+        <v>30897073</v>
       </c>
       <c r="C187" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="188">
@@ -3309,10 +3298,10 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>44160126</v>
+        <v>31260568</v>
       </c>
       <c r="C188" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="189">
@@ -3322,10 +3311,10 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>44673615</v>
+        <v>31624063</v>
       </c>
       <c r="C189" t="n">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="190">
@@ -3335,10 +3324,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>45187105</v>
+        <v>31987558</v>
       </c>
       <c r="C190" t="n">
-        <v>0.66</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="191">
@@ -3348,10 +3337,10 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>45700595</v>
+        <v>32351053</v>
       </c>
       <c r="C191" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="192">
@@ -3361,10 +3350,10 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>46214085</v>
+        <v>32714548</v>
       </c>
       <c r="C192" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="193">
@@ -3374,10 +3363,10 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>46727575</v>
+        <v>33078043</v>
       </c>
       <c r="C193" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="194">
@@ -3387,10 +3376,10 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>47241065</v>
+        <v>33441538</v>
       </c>
       <c r="C194" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="195">
@@ -3400,10 +3389,10 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>47754554</v>
+        <v>33805033</v>
       </c>
       <c r="C195" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="196">
@@ -3413,10 +3402,10 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>48268044</v>
+        <v>34168528</v>
       </c>
       <c r="C196" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="197">
@@ -3426,10 +3415,10 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>48781534</v>
+        <v>34532023</v>
       </c>
       <c r="C197" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="198">
@@ -3439,10 +3428,10 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>49295024</v>
+        <v>34895518</v>
       </c>
       <c r="C198" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="199">
@@ -3452,10 +3441,10 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>49808514</v>
+        <v>35259013</v>
       </c>
       <c r="C199" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="200">
@@ -3465,7 +3454,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>50322004</v>
+        <v>35622508</v>
       </c>
       <c r="C200" t="n">
         <v>0.52</v>
@@ -3478,7 +3467,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>50835493</v>
+        <v>35986003</v>
       </c>
       <c r="C201" t="n">
         <v>0.5</v>
@@ -3494,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="C202" t="n">
-        <v>71.18000000000001</v>
+        <v>71.37</v>
       </c>
     </row>
     <row r="203">
@@ -3504,10 +3493,10 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>225771</v>
+        <v>163839</v>
       </c>
       <c r="C203" t="n">
-        <v>68.55</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="204">
@@ -3517,10 +3506,10 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>451541</v>
+        <v>327678</v>
       </c>
       <c r="C204" t="n">
-        <v>62.03</v>
+        <v>66.81</v>
       </c>
     </row>
     <row r="205">
@@ -3530,10 +3519,10 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>677312</v>
+        <v>491517</v>
       </c>
       <c r="C205" t="n">
-        <v>55.18</v>
+        <v>62.85</v>
       </c>
     </row>
     <row r="206">
@@ -3543,10 +3532,10 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>903083</v>
+        <v>655356</v>
       </c>
       <c r="C206" t="n">
-        <v>48.97</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="207">
@@ -3556,10 +3545,10 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>1128853</v>
+        <v>819195</v>
       </c>
       <c r="C207" t="n">
-        <v>43.71</v>
+        <v>54.86</v>
       </c>
     </row>
     <row r="208">
@@ -3569,10 +3558,10 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>1354624</v>
+        <v>983034</v>
       </c>
       <c r="C208" t="n">
-        <v>38.98</v>
+        <v>51.23</v>
       </c>
     </row>
     <row r="209">
@@ -3582,10 +3571,10 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1580395</v>
+        <v>1146874</v>
       </c>
       <c r="C209" t="n">
-        <v>34.99</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="210">
@@ -3595,10 +3584,10 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1806165</v>
+        <v>1310713</v>
       </c>
       <c r="C210" t="n">
-        <v>31.58</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="211">
@@ -3608,10 +3597,10 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>2031936</v>
+        <v>1474552</v>
       </c>
       <c r="C211" t="n">
-        <v>28.62</v>
+        <v>41.85</v>
       </c>
     </row>
     <row r="212">
@@ -3621,10 +3610,10 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>2257707</v>
+        <v>1638391</v>
       </c>
       <c r="C212" t="n">
-        <v>25.94</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="213">
@@ -3634,10 +3623,10 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>2483477</v>
+        <v>1802230</v>
       </c>
       <c r="C213" t="n">
-        <v>23.7</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="214">
@@ -3647,10 +3636,10 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>2709248</v>
+        <v>1966069</v>
       </c>
       <c r="C214" t="n">
-        <v>21.7</v>
+        <v>34.31</v>
       </c>
     </row>
     <row r="215">
@@ -3660,10 +3649,10 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>2935019</v>
+        <v>2129908</v>
       </c>
       <c r="C215" t="n">
-        <v>19.91</v>
+        <v>32.11</v>
       </c>
     </row>
     <row r="216">
@@ -3673,10 +3662,10 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>3160789</v>
+        <v>2293747</v>
       </c>
       <c r="C216" t="n">
-        <v>18.33</v>
+        <v>30.12</v>
       </c>
     </row>
     <row r="217">
@@ -3686,10 +3675,10 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>3386560</v>
+        <v>2457586</v>
       </c>
       <c r="C217" t="n">
-        <v>16.93</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="218">
@@ -3699,10 +3688,10 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>3612330</v>
+        <v>2621425</v>
       </c>
       <c r="C218" t="n">
-        <v>15.64</v>
+        <v>26.55</v>
       </c>
     </row>
     <row r="219">
@@ -3712,10 +3701,10 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>3838101</v>
+        <v>2785264</v>
       </c>
       <c r="C219" t="n">
-        <v>14.45</v>
+        <v>24.89</v>
       </c>
     </row>
     <row r="220">
@@ -3725,10 +3714,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>4063872</v>
+        <v>2949103</v>
       </c>
       <c r="C220" t="n">
-        <v>13.38</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="221">
@@ -3738,10 +3727,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>4289642</v>
+        <v>3112942</v>
       </c>
       <c r="C221" t="n">
-        <v>12.48</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="222">
@@ -3751,10 +3740,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>4515413</v>
+        <v>3276782</v>
       </c>
       <c r="C222" t="n">
-        <v>11.65</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="223">
@@ -3764,10 +3753,10 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>4741184</v>
+        <v>3440621</v>
       </c>
       <c r="C223" t="n">
-        <v>10.87</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="224">
@@ -3777,10 +3766,10 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>4966954</v>
+        <v>3604460</v>
       </c>
       <c r="C224" t="n">
-        <v>10.18</v>
+        <v>18.23</v>
       </c>
     </row>
     <row r="225">
@@ -3790,10 +3779,10 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>5192725</v>
+        <v>3768299</v>
       </c>
       <c r="C225" t="n">
-        <v>9.539999999999999</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="226">
@@ -3803,10 +3792,10 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>5418496</v>
+        <v>3932138</v>
       </c>
       <c r="C226" t="n">
-        <v>8.93</v>
+        <v>16.09</v>
       </c>
     </row>
     <row r="227">
@@ -3816,10 +3805,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>5644266</v>
+        <v>4095977</v>
       </c>
       <c r="C227" t="n">
-        <v>8.4</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="228">
@@ -3829,10 +3818,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>5870037</v>
+        <v>4259816</v>
       </c>
       <c r="C228" t="n">
-        <v>7.92</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="229">
@@ -3842,10 +3831,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>6095808</v>
+        <v>4423655</v>
       </c>
       <c r="C229" t="n">
-        <v>7.47</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="230">
@@ -3855,10 +3844,10 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>6321578</v>
+        <v>4587494</v>
       </c>
       <c r="C230" t="n">
-        <v>7.03</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="231">
@@ -3868,10 +3857,10 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>6547349</v>
+        <v>4751333</v>
       </c>
       <c r="C231" t="n">
-        <v>6.66</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="232">
@@ -3881,10 +3870,10 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>6773120</v>
+        <v>4915172</v>
       </c>
       <c r="C232" t="n">
-        <v>6.29</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="233">
@@ -3894,10 +3883,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>6998890</v>
+        <v>5079011</v>
       </c>
       <c r="C233" t="n">
-        <v>5.94</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="234">
@@ -3907,10 +3896,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>7224661</v>
+        <v>5242851</v>
       </c>
       <c r="C234" t="n">
-        <v>5.64</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="235">
@@ -3920,10 +3909,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>7450432</v>
+        <v>5406690</v>
       </c>
       <c r="C235" t="n">
-        <v>5.38</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="236">
@@ -3933,10 +3922,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>7676202</v>
+        <v>5570529</v>
       </c>
       <c r="C236" t="n">
-        <v>5.11</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="237">
@@ -3946,10 +3935,10 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>7901973</v>
+        <v>5734368</v>
       </c>
       <c r="C237" t="n">
-        <v>4.86</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="238">
@@ -3959,10 +3948,10 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>8127744</v>
+        <v>5898207</v>
       </c>
       <c r="C238" t="n">
-        <v>4.61</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="239">
@@ -3972,10 +3961,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>8353514</v>
+        <v>6062046</v>
       </c>
       <c r="C239" t="n">
-        <v>4.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="240">
@@ -3985,10 +3974,10 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>8579285</v>
+        <v>6225885</v>
       </c>
       <c r="C240" t="n">
-        <v>4.17</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="241">
@@ -3998,10 +3987,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>8805056</v>
+        <v>6389724</v>
       </c>
       <c r="C241" t="n">
-        <v>3.96</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="242">
@@ -4011,10 +4000,10 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>9030826</v>
+        <v>6553563</v>
       </c>
       <c r="C242" t="n">
-        <v>3.77</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="243">
@@ -4024,10 +4013,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>9256597</v>
+        <v>6717402</v>
       </c>
       <c r="C243" t="n">
-        <v>3.6</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="244">
@@ -4037,10 +4026,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>9482367</v>
+        <v>6881241</v>
       </c>
       <c r="C244" t="n">
-        <v>3.41</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="245">
@@ -4050,10 +4039,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>9708138</v>
+        <v>7045080</v>
       </c>
       <c r="C245" t="n">
-        <v>3.27</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="246">
@@ -4063,10 +4052,10 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>9933909</v>
+        <v>7208919</v>
       </c>
       <c r="C246" t="n">
-        <v>3.12</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="247">
@@ -4076,10 +4065,10 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>10159679</v>
+        <v>7372759</v>
       </c>
       <c r="C247" t="n">
-        <v>2.99</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="248">
@@ -4089,10 +4078,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>10385450</v>
+        <v>7536598</v>
       </c>
       <c r="C248" t="n">
-        <v>2.88</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="249">
@@ -4102,10 +4091,10 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>10611221</v>
+        <v>7700437</v>
       </c>
       <c r="C249" t="n">
-        <v>2.72</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="250">
@@ -4115,10 +4104,10 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>10836991</v>
+        <v>7864276</v>
       </c>
       <c r="C250" t="n">
-        <v>2.61</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="251">
@@ -4128,10 +4117,10 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>11062762</v>
+        <v>8028115</v>
       </c>
       <c r="C251" t="n">
-        <v>2.49</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="252">
@@ -4141,10 +4130,10 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>11288533</v>
+        <v>8191954</v>
       </c>
       <c r="C252" t="n">
-        <v>2.39</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="253">
@@ -4154,10 +4143,10 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>11514303</v>
+        <v>8355793</v>
       </c>
       <c r="C253" t="n">
-        <v>2.29</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="254">
@@ -4167,10 +4156,10 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>11740074</v>
+        <v>8519632</v>
       </c>
       <c r="C254" t="n">
-        <v>2.21</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="255">
@@ -4180,10 +4169,10 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>11965845</v>
+        <v>8683471</v>
       </c>
       <c r="C255" t="n">
-        <v>2.12</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="256">
@@ -4193,10 +4182,10 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>12191615</v>
+        <v>8847310</v>
       </c>
       <c r="C256" t="n">
-        <v>2.04</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="257">
@@ -4206,10 +4195,10 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>12417386</v>
+        <v>9011149</v>
       </c>
       <c r="C257" t="n">
-        <v>1.97</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="258">
@@ -4219,10 +4208,10 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>12643157</v>
+        <v>9174988</v>
       </c>
       <c r="C258" t="n">
-        <v>1.9</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="259">
@@ -4232,10 +4221,10 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>12868927</v>
+        <v>9338827</v>
       </c>
       <c r="C259" t="n">
-        <v>1.82</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="260">
@@ -4245,10 +4234,10 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>13094698</v>
+        <v>9502667</v>
       </c>
       <c r="C260" t="n">
-        <v>1.75</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="261">
@@ -4258,10 +4247,10 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>13320469</v>
+        <v>9666506</v>
       </c>
       <c r="C261" t="n">
-        <v>1.68</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="262">
@@ -4271,10 +4260,10 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>13546239</v>
+        <v>9830345</v>
       </c>
       <c r="C262" t="n">
-        <v>1.62</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="263">
@@ -4284,10 +4273,10 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>13772010</v>
+        <v>9994184</v>
       </c>
       <c r="C263" t="n">
-        <v>1.57</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="264">
@@ -4297,10 +4286,10 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>13997781</v>
+        <v>10158023</v>
       </c>
       <c r="C264" t="n">
-        <v>1.53</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="265">
@@ -4310,10 +4299,10 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>14223551</v>
+        <v>10321862</v>
       </c>
       <c r="C265" t="n">
-        <v>1.47</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="266">
@@ -4323,10 +4312,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>14449322</v>
+        <v>10485701</v>
       </c>
       <c r="C266" t="n">
-        <v>1.41</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="267">
@@ -4336,10 +4325,10 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>14675093</v>
+        <v>10649540</v>
       </c>
       <c r="C267" t="n">
-        <v>1.36</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="268">
@@ -4349,10 +4338,10 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>14900863</v>
+        <v>10813379</v>
       </c>
       <c r="C268" t="n">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="269">
@@ -4362,10 +4351,10 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>15126634</v>
+        <v>10977218</v>
       </c>
       <c r="C269" t="n">
-        <v>1.27</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="270">
@@ -4375,10 +4364,10 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>15352404</v>
+        <v>11141057</v>
       </c>
       <c r="C270" t="n">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="271">
@@ -4388,10 +4377,10 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>15578175</v>
+        <v>11304896</v>
       </c>
       <c r="C271" t="n">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="272">
@@ -4401,10 +4390,10 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>15803946</v>
+        <v>11468736</v>
       </c>
       <c r="C272" t="n">
-        <v>1.16</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="273">
@@ -4414,10 +4403,10 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>16029716</v>
+        <v>11632575</v>
       </c>
       <c r="C273" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="274">
@@ -4427,10 +4416,10 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>16255487</v>
+        <v>11796414</v>
       </c>
       <c r="C274" t="n">
-        <v>1.08</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="275">
@@ -4440,10 +4429,10 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>16481258</v>
+        <v>11960253</v>
       </c>
       <c r="C275" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="276">
@@ -4453,10 +4442,10 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>16707028</v>
+        <v>12124092</v>
       </c>
       <c r="C276" t="n">
-        <v>1</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="277">
@@ -4466,10 +4455,10 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>16932799</v>
+        <v>12287931</v>
       </c>
       <c r="C277" t="n">
-        <v>0.98</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="278">
@@ -4479,10 +4468,10 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>17158570</v>
+        <v>12451770</v>
       </c>
       <c r="C278" t="n">
-        <v>0.96</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="279">
@@ -4492,10 +4481,10 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>17384340</v>
+        <v>12615609</v>
       </c>
       <c r="C279" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="280">
@@ -4505,10 +4494,10 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>17610111</v>
+        <v>12779448</v>
       </c>
       <c r="C280" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="281">
@@ -4518,10 +4507,10 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>17835882</v>
+        <v>12943287</v>
       </c>
       <c r="C281" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="282">
@@ -4531,10 +4520,10 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>18061652</v>
+        <v>13107126</v>
       </c>
       <c r="C282" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="283">
@@ -4544,10 +4533,10 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>18287423</v>
+        <v>13270965</v>
       </c>
       <c r="C283" t="n">
-        <v>0.83</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="284">
@@ -4557,10 +4546,10 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>18513194</v>
+        <v>13434804</v>
       </c>
       <c r="C284" t="n">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="285">
@@ -4570,10 +4559,10 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>18738964</v>
+        <v>13598644</v>
       </c>
       <c r="C285" t="n">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="286">
@@ -4583,10 +4572,10 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>18964735</v>
+        <v>13762483</v>
       </c>
       <c r="C286" t="n">
-        <v>0.74</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="287">
@@ -4596,10 +4585,10 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>19190506</v>
+        <v>13926322</v>
       </c>
       <c r="C287" t="n">
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="288">
@@ -4609,10 +4598,10 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>19416276</v>
+        <v>14090161</v>
       </c>
       <c r="C288" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="289">
@@ -4622,10 +4611,10 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>19642047</v>
+        <v>14254000</v>
       </c>
       <c r="C289" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="290">
@@ -4635,10 +4624,10 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>19867818</v>
+        <v>14417839</v>
       </c>
       <c r="C290" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="291">
@@ -4648,10 +4637,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>20093588</v>
+        <v>14581678</v>
       </c>
       <c r="C291" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="292">
@@ -4661,10 +4650,10 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>20319359</v>
+        <v>14745517</v>
       </c>
       <c r="C292" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="293">
@@ -4674,10 +4663,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>20545130</v>
+        <v>14909356</v>
       </c>
       <c r="C293" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="294">
@@ -4687,10 +4676,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>20770900</v>
+        <v>15073195</v>
       </c>
       <c r="C294" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="295">
@@ -4700,10 +4689,10 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>20996671</v>
+        <v>15237034</v>
       </c>
       <c r="C295" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="296">
@@ -4713,10 +4702,10 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>21222442</v>
+        <v>15400873</v>
       </c>
       <c r="C296" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="297">
@@ -4726,10 +4715,10 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>21448212</v>
+        <v>15564712</v>
       </c>
       <c r="C297" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="298">
@@ -4739,10 +4728,10 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>21673983</v>
+        <v>15728552</v>
       </c>
       <c r="C298" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="299">
@@ -4752,10 +4741,10 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>21899753</v>
+        <v>15892391</v>
       </c>
       <c r="C299" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="300">
@@ -4765,10 +4754,10 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>22125524</v>
+        <v>16056230</v>
       </c>
       <c r="C300" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="301">
@@ -4778,7 +4767,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>22351295</v>
+        <v>16220069</v>
       </c>
       <c r="C301" t="n">
         <v>0.5</v>
@@ -4794,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="C302" t="n">
-        <v>59.19</v>
+        <v>59.41</v>
       </c>
     </row>
     <row r="303">
@@ -4804,10 +4793,10 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>325758</v>
+        <v>251730</v>
       </c>
       <c r="C303" t="n">
-        <v>57.94</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="304">
@@ -4817,10 +4806,10 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>651516</v>
+        <v>503460</v>
       </c>
       <c r="C304" t="n">
-        <v>53.84</v>
+        <v>56.62</v>
       </c>
     </row>
     <row r="305">
@@ -4830,10 +4819,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>977274</v>
+        <v>755190</v>
       </c>
       <c r="C305" t="n">
-        <v>48.96</v>
+        <v>53.49</v>
       </c>
     </row>
     <row r="306">
@@ -4843,10 +4832,10 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>1303032</v>
+        <v>1006920</v>
       </c>
       <c r="C306" t="n">
-        <v>43.99</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="307">
@@ -4856,10 +4845,10 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>1628790</v>
+        <v>1258650</v>
       </c>
       <c r="C307" t="n">
-        <v>39.58</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="308">
@@ -4869,10 +4858,10 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>1954548</v>
+        <v>1510380</v>
       </c>
       <c r="C308" t="n">
-        <v>35.74</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="309">
@@ -4882,10 +4871,10 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>2280306</v>
+        <v>1762110</v>
       </c>
       <c r="C309" t="n">
-        <v>32.25</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="310">
@@ -4895,10 +4884,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>2606064</v>
+        <v>2013840</v>
       </c>
       <c r="C310" t="n">
-        <v>29.23</v>
+        <v>38.36</v>
       </c>
     </row>
     <row r="311">
@@ -4908,10 +4897,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>2931822</v>
+        <v>2265570</v>
       </c>
       <c r="C311" t="n">
-        <v>26.57</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="312">
@@ -4921,10 +4910,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>3257580</v>
+        <v>2517300</v>
       </c>
       <c r="C312" t="n">
-        <v>24.27</v>
+        <v>33.63</v>
       </c>
     </row>
     <row r="313">
@@ -4934,10 +4923,10 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>3583338</v>
+        <v>2769030</v>
       </c>
       <c r="C313" t="n">
-        <v>22.2</v>
+        <v>31.52</v>
       </c>
     </row>
     <row r="314">
@@ -4947,10 +4936,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>3909096</v>
+        <v>3020760</v>
       </c>
       <c r="C314" t="n">
-        <v>20.37</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="315">
@@ -4960,10 +4949,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>4234854</v>
+        <v>3272490</v>
       </c>
       <c r="C315" t="n">
-        <v>18.7</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="316">
@@ -4973,10 +4962,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>4560612</v>
+        <v>3524220</v>
       </c>
       <c r="C316" t="n">
-        <v>17.21</v>
+        <v>25.93</v>
       </c>
     </row>
     <row r="317">
@@ -4986,10 +4975,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>4886370</v>
+        <v>3775949</v>
       </c>
       <c r="C317" t="n">
-        <v>15.88</v>
+        <v>24.37</v>
       </c>
     </row>
     <row r="318">
@@ -4999,10 +4988,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>5212128</v>
+        <v>4027679</v>
       </c>
       <c r="C318" t="n">
-        <v>14.69</v>
+        <v>23</v>
       </c>
     </row>
     <row r="319">
@@ -5012,10 +5001,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>5537886</v>
+        <v>4279409</v>
       </c>
       <c r="C319" t="n">
-        <v>13.62</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="320">
@@ -5025,10 +5014,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>5863644</v>
+        <v>4531139</v>
       </c>
       <c r="C320" t="n">
-        <v>12.7</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="321">
@@ -5038,10 +5027,10 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>6189402</v>
+        <v>4782869</v>
       </c>
       <c r="C321" t="n">
-        <v>11.81</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="322">
@@ -5051,10 +5040,10 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>6515160</v>
+        <v>5034599</v>
       </c>
       <c r="C322" t="n">
-        <v>11.06</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="323">
@@ -5064,10 +5053,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>6840918</v>
+        <v>5286329</v>
       </c>
       <c r="C323" t="n">
-        <v>10.33</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="324">
@@ -5077,10 +5066,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>7166676</v>
+        <v>5538059</v>
       </c>
       <c r="C324" t="n">
-        <v>9.609999999999999</v>
+        <v>16.09</v>
       </c>
     </row>
     <row r="325">
@@ -5090,10 +5079,10 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>7492434</v>
+        <v>5789789</v>
       </c>
       <c r="C325" t="n">
-        <v>9</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="326">
@@ -5103,10 +5092,10 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>7818192</v>
+        <v>6041519</v>
       </c>
       <c r="C326" t="n">
-        <v>8.49</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="327">
@@ -5116,10 +5105,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>8143950</v>
+        <v>6293249</v>
       </c>
       <c r="C327" t="n">
-        <v>7.95</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="328">
@@ -5129,10 +5118,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>8469708</v>
+        <v>6544979</v>
       </c>
       <c r="C328" t="n">
-        <v>7.54</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="329">
@@ -5142,10 +5131,10 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>8795466</v>
+        <v>6796709</v>
       </c>
       <c r="C329" t="n">
-        <v>7.06</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="330">
@@ -5155,10 +5144,10 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>9121224</v>
+        <v>7048439</v>
       </c>
       <c r="C330" t="n">
-        <v>6.67</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="331">
@@ -5168,10 +5157,10 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>9446982</v>
+        <v>7300169</v>
       </c>
       <c r="C331" t="n">
-        <v>6.3</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="332">
@@ -5181,10 +5170,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>9772740</v>
+        <v>7551899</v>
       </c>
       <c r="C332" t="n">
-        <v>6</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="333">
@@ -5194,10 +5183,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>10098498</v>
+        <v>7803629</v>
       </c>
       <c r="C333" t="n">
-        <v>5.68</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="334">
@@ -5207,10 +5196,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>10424256</v>
+        <v>8055359</v>
       </c>
       <c r="C334" t="n">
-        <v>5.38</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="335">
@@ -5220,10 +5209,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>10750014</v>
+        <v>8307089</v>
       </c>
       <c r="C335" t="n">
-        <v>5.11</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="336">
@@ -5233,10 +5222,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>11075772</v>
+        <v>8558819</v>
       </c>
       <c r="C336" t="n">
-        <v>4.89</v>
+        <v>8.210000000000001</v>
       </c>
     </row>
     <row r="337">
@@ -5246,10 +5235,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>11401530</v>
+        <v>8810549</v>
       </c>
       <c r="C337" t="n">
-        <v>4.66</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="338">
@@ -5259,10 +5248,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>11727288</v>
+        <v>9062279</v>
       </c>
       <c r="C338" t="n">
-        <v>4.42</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="339">
@@ -5272,10 +5261,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>12053046</v>
+        <v>9314009</v>
       </c>
       <c r="C339" t="n">
-        <v>4.21</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="340">
@@ -5285,10 +5274,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>12378804</v>
+        <v>9565739</v>
       </c>
       <c r="C340" t="n">
-        <v>4</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="341">
@@ -5298,10 +5287,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>12704562</v>
+        <v>9817469</v>
       </c>
       <c r="C341" t="n">
-        <v>3.81</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="342">
@@ -5311,10 +5300,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>13030320</v>
+        <v>10069199</v>
       </c>
       <c r="C342" t="n">
-        <v>3.62</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="343">
@@ -5324,10 +5313,10 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>13356078</v>
+        <v>10320929</v>
       </c>
       <c r="C343" t="n">
-        <v>3.45</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="344">
@@ -5337,10 +5326,10 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>13681836</v>
+        <v>10572659</v>
       </c>
       <c r="C344" t="n">
-        <v>3.3</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="345">
@@ -5350,10 +5339,10 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>14007594</v>
+        <v>10824388</v>
       </c>
       <c r="C345" t="n">
-        <v>3.15</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="346">
@@ -5363,10 +5352,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>14333352</v>
+        <v>11076118</v>
       </c>
       <c r="C346" t="n">
-        <v>3.02</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="347">
@@ -5376,10 +5365,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>14659110</v>
+        <v>11327848</v>
       </c>
       <c r="C347" t="n">
-        <v>2.89</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="348">
@@ -5389,10 +5378,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>14984868</v>
+        <v>11579578</v>
       </c>
       <c r="C348" t="n">
-        <v>2.76</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="349">
@@ -5402,10 +5391,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>15310626</v>
+        <v>11831308</v>
       </c>
       <c r="C349" t="n">
-        <v>2.66</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="350">
@@ -5415,10 +5404,10 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>15636384</v>
+        <v>12083038</v>
       </c>
       <c r="C350" t="n">
-        <v>2.58</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="351">
@@ -5428,10 +5417,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>15962142</v>
+        <v>12334768</v>
       </c>
       <c r="C351" t="n">
-        <v>2.48</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="352">
@@ -5441,10 +5430,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>16287900</v>
+        <v>12586498</v>
       </c>
       <c r="C352" t="n">
-        <v>2.38</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="353">
@@ -5454,10 +5443,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>16613658</v>
+        <v>12838228</v>
       </c>
       <c r="C353" t="n">
-        <v>2.29</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="354">
@@ -5467,10 +5456,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>16939416</v>
+        <v>13089958</v>
       </c>
       <c r="C354" t="n">
-        <v>2.21</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="355">
@@ -5480,10 +5469,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>17265174</v>
+        <v>13341688</v>
       </c>
       <c r="C355" t="n">
-        <v>2.13</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="356">
@@ -5493,10 +5482,10 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>17590932</v>
+        <v>13593418</v>
       </c>
       <c r="C356" t="n">
-        <v>2.05</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="357">
@@ -5506,10 +5495,10 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>17916690</v>
+        <v>13845148</v>
       </c>
       <c r="C357" t="n">
-        <v>1.97</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="358">
@@ -5519,10 +5508,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>18242448</v>
+        <v>14096878</v>
       </c>
       <c r="C358" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="359">
@@ -5532,10 +5521,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>18568206</v>
+        <v>14348608</v>
       </c>
       <c r="C359" t="n">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="360">
@@ -5545,10 +5534,10 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>18893964</v>
+        <v>14600338</v>
       </c>
       <c r="C360" t="n">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="361">
@@ -5558,10 +5547,10 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>19219721</v>
+        <v>14852068</v>
       </c>
       <c r="C361" t="n">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="362">
@@ -5571,10 +5560,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>19545479</v>
+        <v>15103798</v>
       </c>
       <c r="C362" t="n">
-        <v>1.66</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="363">
@@ -5584,10 +5573,10 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>19871237</v>
+        <v>15355528</v>
       </c>
       <c r="C363" t="n">
-        <v>1.61</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="364">
@@ -5597,10 +5586,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>20196995</v>
+        <v>15607258</v>
       </c>
       <c r="C364" t="n">
-        <v>1.56</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="365">
@@ -5610,10 +5599,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>20522753</v>
+        <v>15858988</v>
       </c>
       <c r="C365" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="366">
@@ -5623,10 +5612,10 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>20848511</v>
+        <v>16110718</v>
       </c>
       <c r="C366" t="n">
-        <v>1.46</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="367">
@@ -5636,10 +5625,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>21174269</v>
+        <v>16362448</v>
       </c>
       <c r="C367" t="n">
-        <v>1.41</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="368">
@@ -5649,10 +5638,10 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>21500027</v>
+        <v>16614178</v>
       </c>
       <c r="C368" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="369">
@@ -5662,10 +5651,10 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>21825785</v>
+        <v>16865908</v>
       </c>
       <c r="C369" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="370">
@@ -5675,10 +5664,10 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>22151543</v>
+        <v>17117638</v>
       </c>
       <c r="C370" t="n">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="371">
@@ -5688,10 +5677,10 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>22477301</v>
+        <v>17369368</v>
       </c>
       <c r="C371" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="372">
@@ -5701,10 +5690,10 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>22803059</v>
+        <v>17621098</v>
       </c>
       <c r="C372" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="373">
@@ -5714,10 +5703,10 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>23128817</v>
+        <v>17872828</v>
       </c>
       <c r="C373" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="374">
@@ -5727,10 +5716,10 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>23454575</v>
+        <v>18124557</v>
       </c>
       <c r="C374" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="375">
@@ -5740,10 +5729,10 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>23780333</v>
+        <v>18376287</v>
       </c>
       <c r="C375" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="376">
@@ -5753,10 +5742,10 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>24106091</v>
+        <v>18628017</v>
       </c>
       <c r="C376" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="377">
@@ -5766,10 +5755,10 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>24431849</v>
+        <v>18879747</v>
       </c>
       <c r="C377" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="378">
@@ -5779,10 +5768,10 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>24757607</v>
+        <v>19131477</v>
       </c>
       <c r="C378" t="n">
-        <v>0.97</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="379">
@@ -5792,10 +5781,10 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>25083365</v>
+        <v>19383207</v>
       </c>
       <c r="C379" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="380">
@@ -5805,10 +5794,10 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>25409123</v>
+        <v>19634937</v>
       </c>
       <c r="C380" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="381">
@@ -5818,10 +5807,10 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>25734881</v>
+        <v>19886667</v>
       </c>
       <c r="C381" t="n">
-        <v>0.9</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="382">
@@ -5831,10 +5820,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>26060639</v>
+        <v>20138397</v>
       </c>
       <c r="C382" t="n">
-        <v>0.86</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="383">
@@ -5844,10 +5833,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>26386397</v>
+        <v>20390127</v>
       </c>
       <c r="C383" t="n">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="384">
@@ -5857,10 +5846,10 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>26712155</v>
+        <v>20641857</v>
       </c>
       <c r="C384" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="385">
@@ -5870,10 +5859,10 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>27037913</v>
+        <v>20893587</v>
       </c>
       <c r="C385" t="n">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="386">
@@ -5883,10 +5872,10 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>27363671</v>
+        <v>21145317</v>
       </c>
       <c r="C386" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="387">
@@ -5896,10 +5885,10 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>27689429</v>
+        <v>21397047</v>
       </c>
       <c r="C387" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="388">
@@ -5909,10 +5898,10 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>28015187</v>
+        <v>21648777</v>
       </c>
       <c r="C388" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="389">
@@ -5922,10 +5911,10 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>28340945</v>
+        <v>21900507</v>
       </c>
       <c r="C389" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="390">
@@ -5935,10 +5924,10 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>28666703</v>
+        <v>22152237</v>
       </c>
       <c r="C390" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="391">
@@ -5948,10 +5937,10 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>28992461</v>
+        <v>22403967</v>
       </c>
       <c r="C391" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="392">
@@ -5961,10 +5950,10 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>29318219</v>
+        <v>22655697</v>
       </c>
       <c r="C392" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="393">
@@ -5974,10 +5963,10 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>29643977</v>
+        <v>22907427</v>
       </c>
       <c r="C393" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="394">
@@ -5987,10 +5976,10 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>29969735</v>
+        <v>23159157</v>
       </c>
       <c r="C394" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="395">
@@ -6000,10 +5989,10 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>30295493</v>
+        <v>23410887</v>
       </c>
       <c r="C395" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="396">
@@ -6013,10 +6002,10 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>30621251</v>
+        <v>23662617</v>
       </c>
       <c r="C396" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="397">
@@ -6026,10 +6015,10 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>30947009</v>
+        <v>23914347</v>
       </c>
       <c r="C397" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="398">
@@ -6039,7 +6028,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>31272767</v>
+        <v>24166077</v>
       </c>
       <c r="C398" t="n">
         <v>0.55</v>
@@ -6052,7 +6041,7 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>31598525</v>
+        <v>24417807</v>
       </c>
       <c r="C399" t="n">
         <v>0.53</v>
@@ -6065,7 +6054,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>31924283</v>
+        <v>24669537</v>
       </c>
       <c r="C400" t="n">
         <v>0.52</v>
@@ -6078,7 +6067,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>32250041</v>
+        <v>24921267</v>
       </c>
       <c r="C401" t="n">
         <v>0.5</v>
@@ -6094,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="C402" t="n">
-        <v>91.62</v>
+        <v>91.89</v>
       </c>
     </row>
     <row r="403">
@@ -6104,10 +6093,10 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>534978</v>
+        <v>299994</v>
       </c>
       <c r="C403" t="n">
-        <v>79.89</v>
+        <v>88.65000000000001</v>
       </c>
     </row>
     <row r="404">
@@ -6117,10 +6106,10 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>1069956</v>
+        <v>599988</v>
       </c>
       <c r="C404" t="n">
-        <v>66.18000000000001</v>
+        <v>83.73999999999999</v>
       </c>
     </row>
     <row r="405">
@@ -6130,10 +6119,10 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>1604934</v>
+        <v>899983</v>
       </c>
       <c r="C405" t="n">
-        <v>55.5</v>
+        <v>78.65000000000001</v>
       </c>
     </row>
     <row r="406">
@@ -6143,10 +6132,10 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>2139912</v>
+        <v>1199977</v>
       </c>
       <c r="C406" t="n">
-        <v>47.25</v>
+        <v>73.97</v>
       </c>
     </row>
     <row r="407">
@@ -6156,10 +6145,10 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>2674890</v>
+        <v>1499971</v>
       </c>
       <c r="C407" t="n">
-        <v>40.88</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="408">
@@ -6169,10 +6158,10 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>3209868</v>
+        <v>1799965</v>
       </c>
       <c r="C408" t="n">
-        <v>35.78</v>
+        <v>65.03</v>
       </c>
     </row>
     <row r="409">
@@ -6182,10 +6171,10 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>3744847</v>
+        <v>2099960</v>
       </c>
       <c r="C409" t="n">
-        <v>31.59</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="410">
@@ -6195,10 +6184,10 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>4279825</v>
+        <v>2399954</v>
       </c>
       <c r="C410" t="n">
-        <v>28.05</v>
+        <v>56.77</v>
       </c>
     </row>
     <row r="411">
@@ -6208,10 +6197,10 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>4814803</v>
+        <v>2699948</v>
       </c>
       <c r="C411" t="n">
-        <v>25.16</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="412">
@@ -6221,10 +6210,10 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>5349781</v>
+        <v>2999942</v>
       </c>
       <c r="C412" t="n">
-        <v>22.65</v>
+        <v>49.52</v>
       </c>
     </row>
     <row r="413">
@@ -6234,10 +6223,10 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>5884759</v>
+        <v>3299936</v>
       </c>
       <c r="C413" t="n">
-        <v>20.47</v>
+        <v>46.19</v>
       </c>
     </row>
     <row r="414">
@@ -6247,10 +6236,10 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>6419737</v>
+        <v>3599931</v>
       </c>
       <c r="C414" t="n">
-        <v>18.63</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="415">
@@ -6260,10 +6249,10 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>6954715</v>
+        <v>3899925</v>
       </c>
       <c r="C415" t="n">
-        <v>16.94</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="416">
@@ -6273,10 +6262,10 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>7489693</v>
+        <v>4199919</v>
       </c>
       <c r="C416" t="n">
-        <v>15.47</v>
+        <v>37.54</v>
       </c>
     </row>
     <row r="417">
@@ -6286,10 +6275,10 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>8024671</v>
+        <v>4499913</v>
       </c>
       <c r="C417" t="n">
-        <v>14.19</v>
+        <v>35.06</v>
       </c>
     </row>
     <row r="418">
@@ -6299,10 +6288,10 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>8559649</v>
+        <v>4799908</v>
       </c>
       <c r="C418" t="n">
-        <v>13.07</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="419">
@@ -6312,10 +6301,10 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>9094627</v>
+        <v>5099902</v>
       </c>
       <c r="C419" t="n">
-        <v>12.09</v>
+        <v>30.54</v>
       </c>
     </row>
     <row r="420">
@@ -6325,10 +6314,10 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>9629605</v>
+        <v>5399896</v>
       </c>
       <c r="C420" t="n">
-        <v>11.24</v>
+        <v>28.49</v>
       </c>
     </row>
     <row r="421">
@@ -6338,10 +6327,10 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>10164584</v>
+        <v>5699890</v>
       </c>
       <c r="C421" t="n">
-        <v>10.42</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="422">
@@ -6351,10 +6340,10 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>10699562</v>
+        <v>5999885</v>
       </c>
       <c r="C422" t="n">
-        <v>9.710000000000001</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="423">
@@ -6364,10 +6353,10 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>11234540</v>
+        <v>6299879</v>
       </c>
       <c r="C423" t="n">
-        <v>9.050000000000001</v>
+        <v>23.29</v>
       </c>
     </row>
     <row r="424">
@@ -6377,10 +6366,10 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>11769518</v>
+        <v>6599873</v>
       </c>
       <c r="C424" t="n">
-        <v>8.470000000000001</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="425">
@@ -6390,10 +6379,10 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>12304496</v>
+        <v>6899867</v>
       </c>
       <c r="C425" t="n">
-        <v>7.96</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="426">
@@ -6403,10 +6392,10 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>12839474</v>
+        <v>7199861</v>
       </c>
       <c r="C426" t="n">
-        <v>7.51</v>
+        <v>19.14</v>
       </c>
     </row>
     <row r="427">
@@ -6416,10 +6405,10 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>13374452</v>
+        <v>7499856</v>
       </c>
       <c r="C427" t="n">
-        <v>7.04</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="428">
@@ -6429,10 +6418,10 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>13909430</v>
+        <v>7799850</v>
       </c>
       <c r="C428" t="n">
-        <v>6.65</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="429">
@@ -6442,10 +6431,10 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>14444408</v>
+        <v>8099844</v>
       </c>
       <c r="C429" t="n">
-        <v>6.28</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="430">
@@ -6455,10 +6444,10 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>14979386</v>
+        <v>8399838</v>
       </c>
       <c r="C430" t="n">
-        <v>5.93</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="431">
@@ -6468,10 +6457,10 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>15514364</v>
+        <v>8699833</v>
       </c>
       <c r="C431" t="n">
-        <v>5.59</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="432">
@@ -6481,10 +6470,10 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>16049342</v>
+        <v>8999827</v>
       </c>
       <c r="C432" t="n">
-        <v>5.29</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="433">
@@ -6494,10 +6483,10 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>16584320</v>
+        <v>9299821</v>
       </c>
       <c r="C433" t="n">
-        <v>5.02</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="434">
@@ -6507,10 +6496,10 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>17119299</v>
+        <v>9599815</v>
       </c>
       <c r="C434" t="n">
-        <v>4.75</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="435">
@@ -6520,10 +6509,10 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>17654277</v>
+        <v>9899809</v>
       </c>
       <c r="C435" t="n">
-        <v>4.51</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="436">
@@ -6533,10 +6522,10 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>18189255</v>
+        <v>10199804</v>
       </c>
       <c r="C436" t="n">
-        <v>4.3</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="437">
@@ -6546,10 +6535,10 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>18724233</v>
+        <v>10499798</v>
       </c>
       <c r="C437" t="n">
-        <v>4.08</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="438">
@@ -6559,10 +6548,10 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>19259211</v>
+        <v>10799792</v>
       </c>
       <c r="C438" t="n">
-        <v>3.9</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="439">
@@ -6572,10 +6561,10 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>19794189</v>
+        <v>11099786</v>
       </c>
       <c r="C439" t="n">
-        <v>3.7</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="440">
@@ -6585,10 +6574,10 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>20329167</v>
+        <v>11399781</v>
       </c>
       <c r="C440" t="n">
-        <v>3.51</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="441">
@@ -6598,10 +6587,10 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>20864145</v>
+        <v>11699775</v>
       </c>
       <c r="C441" t="n">
-        <v>3.37</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="442">
@@ -6611,10 +6600,10 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>21399123</v>
+        <v>11999769</v>
       </c>
       <c r="C442" t="n">
-        <v>3.22</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="443">
@@ -6624,10 +6613,10 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>21934101</v>
+        <v>12299763</v>
       </c>
       <c r="C443" t="n">
-        <v>3.06</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="444">
@@ -6637,10 +6626,10 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>22469079</v>
+        <v>12599758</v>
       </c>
       <c r="C444" t="n">
-        <v>2.91</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="445">
@@ -6650,10 +6639,10 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>23004057</v>
+        <v>12899752</v>
       </c>
       <c r="C445" t="n">
-        <v>2.78</v>
+        <v>6</v>
       </c>
     </row>
     <row r="446">
@@ -6663,10 +6652,10 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>23539035</v>
+        <v>13199746</v>
       </c>
       <c r="C446" t="n">
-        <v>2.68</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="447">
@@ -6676,10 +6665,10 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>24074014</v>
+        <v>13499740</v>
       </c>
       <c r="C447" t="n">
-        <v>2.57</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="448">
@@ -6689,10 +6678,10 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>24608992</v>
+        <v>13799734</v>
       </c>
       <c r="C448" t="n">
-        <v>2.46</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="449">
@@ -6702,10 +6691,10 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>25143970</v>
+        <v>14099729</v>
       </c>
       <c r="C449" t="n">
-        <v>2.36</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="450">
@@ -6715,10 +6704,10 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>25678948</v>
+        <v>14399723</v>
       </c>
       <c r="C450" t="n">
-        <v>2.27</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="451">
@@ -6728,10 +6717,10 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>26213926</v>
+        <v>14699717</v>
       </c>
       <c r="C451" t="n">
-        <v>2.17</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="452">
@@ -6741,10 +6730,10 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>26748904</v>
+        <v>14999711</v>
       </c>
       <c r="C452" t="n">
-        <v>2.08</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="453">
@@ -6754,10 +6743,10 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>27283882</v>
+        <v>15299706</v>
       </c>
       <c r="C453" t="n">
-        <v>2</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="454">
@@ -6767,10 +6756,10 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>27818860</v>
+        <v>15599700</v>
       </c>
       <c r="C454" t="n">
-        <v>1.92</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="455">
@@ -6780,10 +6769,10 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>28353838</v>
+        <v>15899694</v>
       </c>
       <c r="C455" t="n">
-        <v>1.86</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="456">
@@ -6793,10 +6782,10 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>28888816</v>
+        <v>16199688</v>
       </c>
       <c r="C456" t="n">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="457">
@@ -6806,10 +6795,10 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>29423794</v>
+        <v>16499682</v>
       </c>
       <c r="C457" t="n">
-        <v>1.73</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="458">
@@ -6819,10 +6808,10 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>29958772</v>
+        <v>16799677</v>
       </c>
       <c r="C458" t="n">
-        <v>1.66</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="459">
@@ -6832,10 +6821,10 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>30493751</v>
+        <v>17099671</v>
       </c>
       <c r="C459" t="n">
-        <v>1.6</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="460">
@@ -6845,10 +6834,10 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>31028729</v>
+        <v>17399665</v>
       </c>
       <c r="C460" t="n">
-        <v>1.55</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="461">
@@ -6858,10 +6847,10 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>31563707</v>
+        <v>17699659</v>
       </c>
       <c r="C461" t="n">
-        <v>1.5</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="462">
@@ -6871,10 +6860,10 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>32098685</v>
+        <v>17999654</v>
       </c>
       <c r="C462" t="n">
-        <v>1.45</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="463">
@@ -6884,10 +6873,10 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>32633663</v>
+        <v>18299648</v>
       </c>
       <c r="C463" t="n">
-        <v>1.4</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="464">
@@ -6897,10 +6886,10 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>33168641</v>
+        <v>18599642</v>
       </c>
       <c r="C464" t="n">
-        <v>1.35</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="465">
@@ -6910,10 +6899,10 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>33703619</v>
+        <v>18899636</v>
       </c>
       <c r="C465" t="n">
-        <v>1.31</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="466">
@@ -6923,10 +6912,10 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>34238597</v>
+        <v>19199630</v>
       </c>
       <c r="C466" t="n">
-        <v>1.27</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="467">
@@ -6936,10 +6925,10 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>34773575</v>
+        <v>19499625</v>
       </c>
       <c r="C467" t="n">
-        <v>1.23</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="468">
@@ -6949,10 +6938,10 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>35308553</v>
+        <v>19799619</v>
       </c>
       <c r="C468" t="n">
-        <v>1.19</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="469">
@@ -6962,10 +6951,10 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>35843531</v>
+        <v>20099613</v>
       </c>
       <c r="C469" t="n">
-        <v>1.16</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="470">
@@ -6975,10 +6964,10 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>36378509</v>
+        <v>20399607</v>
       </c>
       <c r="C470" t="n">
-        <v>1.12</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="471">
@@ -6988,10 +6977,10 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>36913487</v>
+        <v>20699602</v>
       </c>
       <c r="C471" t="n">
-        <v>1.07</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="472">
@@ -7001,10 +6990,10 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>37448466</v>
+        <v>20999596</v>
       </c>
       <c r="C472" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="473">
@@ -7014,10 +7003,10 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>37983444</v>
+        <v>21299590</v>
       </c>
       <c r="C473" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="474">
@@ -7027,10 +7016,10 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>38518422</v>
+        <v>21599584</v>
       </c>
       <c r="C474" t="n">
-        <v>0.99</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="475">
@@ -7040,10 +7029,10 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>39053400</v>
+        <v>21899579</v>
       </c>
       <c r="C475" t="n">
-        <v>0.96</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="476">
@@ -7053,10 +7042,10 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>39588378</v>
+        <v>22199573</v>
       </c>
       <c r="C476" t="n">
-        <v>0.93</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="477">
@@ -7066,10 +7055,10 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>40123356</v>
+        <v>22499567</v>
       </c>
       <c r="C477" t="n">
-        <v>0.91</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="478">
@@ -7079,10 +7068,10 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>40658334</v>
+        <v>22799561</v>
       </c>
       <c r="C478" t="n">
-        <v>0.89</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="479">
@@ -7092,10 +7081,10 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>41193312</v>
+        <v>23099555</v>
       </c>
       <c r="C479" t="n">
-        <v>0.86</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="480">
@@ -7105,10 +7094,10 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>41728290</v>
+        <v>23399550</v>
       </c>
       <c r="C480" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="481">
@@ -7118,10 +7107,10 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>42263268</v>
+        <v>23699544</v>
       </c>
       <c r="C481" t="n">
-        <v>0.82</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="482">
@@ -7131,10 +7120,10 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>42798246</v>
+        <v>23999538</v>
       </c>
       <c r="C482" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483">
@@ -7144,10 +7133,10 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>43333224</v>
+        <v>24299532</v>
       </c>
       <c r="C483" t="n">
-        <v>0.79</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="484">
@@ -7157,10 +7146,10 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>43868202</v>
+        <v>24599527</v>
       </c>
       <c r="C484" t="n">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="485">
@@ -7170,10 +7159,10 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>44403181</v>
+        <v>24899521</v>
       </c>
       <c r="C485" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="486">
@@ -7183,10 +7172,10 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>44938159</v>
+        <v>25199515</v>
       </c>
       <c r="C486" t="n">
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="487">
@@ -7196,10 +7185,10 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>45473137</v>
+        <v>25499509</v>
       </c>
       <c r="C487" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="488">
@@ -7209,10 +7198,10 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>46008115</v>
+        <v>25799503</v>
       </c>
       <c r="C488" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="489">
@@ -7222,10 +7211,10 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>46543093</v>
+        <v>26099498</v>
       </c>
       <c r="C489" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="490">
@@ -7235,10 +7224,10 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>47078071</v>
+        <v>26399492</v>
       </c>
       <c r="C490" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="491">
@@ -7248,10 +7237,10 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>47613049</v>
+        <v>26699486</v>
       </c>
       <c r="C491" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="492">
@@ -7261,10 +7250,10 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>48148027</v>
+        <v>26999480</v>
       </c>
       <c r="C492" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="493">
@@ -7274,10 +7263,10 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>48683005</v>
+        <v>27299475</v>
       </c>
       <c r="C493" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="494">
@@ -7287,10 +7276,10 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>49217983</v>
+        <v>27599469</v>
       </c>
       <c r="C494" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="495">
@@ -7300,10 +7289,10 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>49752961</v>
+        <v>27899463</v>
       </c>
       <c r="C495" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="496">
@@ -7313,10 +7302,10 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>50287939</v>
+        <v>28199457</v>
       </c>
       <c r="C496" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="497">
@@ -7326,10 +7315,10 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>50822918</v>
+        <v>28499451</v>
       </c>
       <c r="C497" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="498">
@@ -7339,10 +7328,10 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>51357896</v>
+        <v>28799446</v>
       </c>
       <c r="C498" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="499">
@@ -7352,10 +7341,10 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>51892874</v>
+        <v>29099440</v>
       </c>
       <c r="C499" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="500">
@@ -7365,10 +7354,10 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>52427852</v>
+        <v>29399434</v>
       </c>
       <c r="C500" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="501">
@@ -7378,7 +7367,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>52962830</v>
+        <v>29699428</v>
       </c>
       <c r="C501" t="n">
         <v>0.5</v>
@@ -7398,38 +7387,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>function_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>rationale</t>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Govern</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>No formal cybersecurity policy exists</t>
+          <t>No data yet - run the relevant module first</t>
         </is>
       </c>
     </row>
@@ -7478,94 +7449,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>vendor_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>service_type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>criticality</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>risk_tier</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>gap_count</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>critical_gaps</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>assessor</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>assessment_date</t>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>acme</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Payment Processor</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ameeer</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
+          <t>No data yet - run the relevant module first</t>
         </is>
       </c>
     </row>
@@ -7583,29 +7480,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>risk_tier</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>vendor_count</t>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
+          <t>No data yet - run the relevant module first</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/dashboards/grc_powerbi_data.xlsx
+++ b/dashboards/grc_powerbi_data.xlsx
@@ -13,6 +13,7 @@
     <sheet name="ControlGaps" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="VendorAssessments" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="VendorTierSummary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="KPISummary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -130,9 +131,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RiskScenarios_tbl" displayName="RiskScenarios_tbl" ref="A1:O6" headerRowCount="1">
-  <autoFilter ref="A1:O6"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RiskScenarios_tbl" displayName="RiskScenarios_tbl" ref="A1:S6" headerRowCount="1">
+  <autoFilter ref="A1:S6"/>
+  <tableColumns count="19">
     <tableColumn id="1" name="scenario_name"/>
     <tableColumn id="2" name="loss_low"/>
     <tableColumn id="3" name="loss_high"/>
@@ -145,9 +146,13 @@
     <tableColumn id="10" name="prob_over_1m"/>
     <tableColumn id="11" name="prob_over_5m"/>
     <tableColumn id="12" name="control_cost"/>
-    <tableColumn id="13" name="avg_frequency"/>
-    <tableColumn id="14" name="likelihood_band"/>
-    <tableColumn id="15" name="impact_band"/>
+    <tableColumn id="13" name="control_effectiveness"/>
+    <tableColumn id="14" name="residual_ale"/>
+    <tableColumn id="15" name="rosi"/>
+    <tableColumn id="16" name="avg_frequency"/>
+    <tableColumn id="17" name="likelihood_band"/>
+    <tableColumn id="18" name="impact_band"/>
+    <tableColumn id="19" name="rosi_pct"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -166,40 +171,79 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CSFScores_tbl" displayName="CSFScores_tbl" ref="A1:A2" headerRowCount="1">
-  <autoFilter ref="A1:A2"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="note"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CSFScores_tbl" displayName="CSFScores_tbl" ref="A1:E7" headerRowCount="1">
+  <autoFilter ref="A1:E7"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="function_name"/>
+    <tableColumn id="2" name="score"/>
+    <tableColumn id="3" name="target_score"/>
+    <tableColumn id="4" name="rationale"/>
+    <tableColumn id="5" name="gap_to_target"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ControlGaps_tbl" displayName="ControlGaps_tbl" ref="A1:A2" headerRowCount="1">
-  <autoFilter ref="A1:A2"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="note"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ControlGaps_tbl" displayName="ControlGaps_tbl" ref="A1:F5" headerRowCount="1">
+  <autoFilter ref="A1:F5"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="function_name"/>
+    <tableColumn id="2" name="gap_description"/>
+    <tableColumn id="3" name="priority"/>
+    <tableColumn id="4" name="nist_ref"/>
+    <tableColumn id="5" name="iso27001_ref"/>
+    <tableColumn id="6" name="soc2_ref"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="VendorAssessments_tbl" displayName="VendorAssessments_tbl" ref="A1:A2" headerRowCount="1">
-  <autoFilter ref="A1:A2"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="note"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="VendorAssessments_tbl" displayName="VendorAssessments_tbl" ref="A1:M9" headerRowCount="1">
+  <autoFilter ref="A1:M9"/>
+  <tableColumns count="13">
+    <tableColumn id="1" name="vendor_name"/>
+    <tableColumn id="2" name="service_type"/>
+    <tableColumn id="3" name="criticality"/>
+    <tableColumn id="4" name="risk_tier"/>
+    <tableColumn id="5" name="score"/>
+    <tableColumn id="6" name="gap_count"/>
+    <tableColumn id="7" name="critical_gaps"/>
+    <tableColumn id="8" name="assessor"/>
+    <tableColumn id="9" name="assessment_date"/>
+    <tableColumn id="10" name="reassessment_window_days"/>
+    <tableColumn id="11" name="days_since_assessment"/>
+    <tableColumn id="12" name="reassessment_due"/>
+    <tableColumn id="13" name="is_overdue"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="VendorTierSummary_tbl" displayName="VendorTierSummary_tbl" ref="A1:A2" headerRowCount="1">
-  <autoFilter ref="A1:A2"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="note"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="VendorTierSummary_tbl" displayName="VendorTierSummary_tbl" ref="A1:B5" headerRowCount="1">
+  <autoFilter ref="A1:B5"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="risk_tier"/>
+    <tableColumn id="2" name="vendor_count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="KPISummary_tbl" displayName="KPISummary_tbl" ref="A1:H2" headerRowCount="1">
+  <autoFilter ref="A1:H2"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="vendors_assessed"/>
+    <tableColumn id="2" name="critical_vendors"/>
+    <tableColumn id="3" name="overdue_vendors"/>
+    <tableColumn id="4" name="avg_vendor_score"/>
+    <tableColumn id="5" name="csf_overall_score"/>
+    <tableColumn id="6" name="total_ale"/>
+    <tableColumn id="7" name="total_residual_ale"/>
+    <tableColumn id="8" name="compliance_posture_score"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -494,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,17 +604,37 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>control_effectiveness</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>residual_ale</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>rosi</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>avg_frequency</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>likelihood_band</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>impact_band</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rosi_pct</t>
         </is>
       </c>
     </row>
@@ -614,17 +678,29 @@
         <v>350000</v>
       </c>
       <c r="M2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1491282</v>
+      </c>
+      <c r="O2" t="n">
+        <v>8.94187871783774</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.75</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
+      </c>
+      <c r="S2" t="n">
+        <v>894</v>
       </c>
     </row>
     <row r="3">
@@ -667,17 +743,29 @@
         <v>500000</v>
       </c>
       <c r="M3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1354961</v>
+      </c>
+      <c r="O3" t="n">
+        <v>7.129763936088877</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.25</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
+      </c>
+      <c r="S3" t="n">
+        <v>713</v>
       </c>
     </row>
     <row r="4">
@@ -720,17 +808,29 @@
         <v>280000</v>
       </c>
       <c r="M4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N4" t="n">
+        <v>705962</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.682397913752179</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.25</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
+      </c>
+      <c r="S4" t="n">
+        <v>368</v>
       </c>
     </row>
     <row r="5">
@@ -773,17 +873,29 @@
         <v>200000</v>
       </c>
       <c r="M5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1081196</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7.108970962607609</v>
+      </c>
+      <c r="P5" t="n">
         <v>0.9</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
+      </c>
+      <c r="S5" t="n">
+        <v>711</v>
       </c>
     </row>
     <row r="6">
@@ -826,17 +938,29 @@
         <v>180000</v>
       </c>
       <c r="M6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>892842</v>
+      </c>
+      <c r="O6" t="n">
+        <v>18.84094325080703</v>
+      </c>
+      <c r="P6" t="n">
         <v>2.5</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
+      </c>
+      <c r="S6" t="n">
+        <v>1884</v>
       </c>
     </row>
   </sheetData>
@@ -7387,21 +7511,160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>function_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>target_score</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>rationale</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>gap_to_target</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No data yet - run the relevant module first</t>
-        </is>
+          <t>Govern</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Security policy exists but is three years old and was never re-approved. No documented risk appetite statement.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Asset inventory is a spreadsheet maintained by hand and is known to be incomplete for cloud workloads.</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MFA enforced on email and remote access, data encrypted at rest and in transit. Access reviews happen but are not evidenced.</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Detect</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Logs are collected centrally but nobody owns alert triage. No defined thresholds and no measured time to detect.</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Respond</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>No documented incident response plan. The 24-hour OSFI reporting path has never been walked through.</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Recover</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Backups tested quarterly and RTOs defined for the core banking platform. Wider BCP not exercised this year.</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7418,20 +7681,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>function_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>gap_description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>nist_ref</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>iso27001_ref</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>soc2_ref</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No data yet - run the relevant module first</t>
+          <t>Govern</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>No formal cybersecurity governance framework in place.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>GV.PO-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>A.5.1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CC1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Incomplete or missing asset inventory and risk assessment.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ID.AM-01</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>A.5.9</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CC6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Detect</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Insufficient monitoring — security events may go unnoticed.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DE.CM-01</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>A.8.15, A.8.16</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CC7.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Respond</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>No documented or tested incident response plan.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RS.MA-01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>A.5.24, A.5.26</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CC7.3</t>
         </is>
       </c>
     </row>
@@ -7449,21 +7858,514 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>vendor_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>service_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>criticality</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>risk_tier</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>gap_count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>critical_gaps</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>assessor</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>assessment_date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>reassessment_window_days</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>days_since_assessment</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>reassessment_due</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>is_overdue</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No data yet - run the relevant module first</t>
-        </is>
+          <t>NorthPeak Cloud Services</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cloud Provider</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ameer Khan</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>730</v>
+      </c>
+      <c r="K2" t="n">
+        <v>200</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2028-03-04</t>
+        </is>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MapleLedger Payments</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Payment Processor</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>72</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ameer Khan</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>365</v>
+      </c>
+      <c r="K3" t="n">
+        <v>45</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2027-08-07</t>
+        </is>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Borealis Analytics</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Data Analytics / AI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>45</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ameer Khan</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>90</v>
+      </c>
+      <c r="K4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rideau Infrastructure Group</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>34</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ameer Khan</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>90</v>
+      </c>
+      <c r="K5" t="n">
+        <v>220</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cartier Ledger Systems</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Software / SaaS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>72</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ameer Khan</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>365</v>
+      </c>
+      <c r="K6" t="n">
+        <v>80</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2027-07-03</t>
+        </is>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lakeshore Trust Software</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Software / SaaS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ameer Khan</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>730</v>
+      </c>
+      <c r="K7" t="n">
+        <v>120</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2028-05-23</t>
+        </is>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gastown Data Works</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Data Analytics / AI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>65</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ameer Khan</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>365</v>
+      </c>
+      <c r="K8" t="n">
+        <v>400</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Acadia Payment Networks</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Payment Processor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ameer Khan</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>90</v>
+      </c>
+      <c r="K9" t="n">
+        <v>140</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7480,21 +8382,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>risk_tier</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>vendor_count</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No data yet - run the relevant module first</t>
-        </is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>vendors_assessed</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>critical_vendors</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>overdue_vendors</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>avg_vendor_score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>csf_overall_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_ale</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>total_residual_ale</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>compliance_posture_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="F2" t="n">
+        <v>19575017</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5526243</v>
+      </c>
+      <c r="H2" t="n">
+        <v>53.8</v>
       </c>
     </row>
   </sheetData>

--- a/dashboards/grc_powerbi_data.xlsx
+++ b/dashboards/grc_powerbi_data.xlsx
@@ -7555,7 +7555,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Security policy exists but is three years old and was never re-approved. No documented risk appetite statement.</t>
+          <t>Policy is three years old and was never re-approved. Risk appetite undocumented.</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Asset inventory is a spreadsheet maintained by hand and is known to be incomplete for cloud workloads.</t>
+          <t>Asset inventory hand-maintained and incomplete for cloud. Risk assessment informal.</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MFA enforced on email and remote access, data encrypted at rest and in transit. Access reviews happen but are not evidenced.</t>
+          <t>MFA and encryption deployed. Access reviews run but are not evidenced.</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Logs are collected centrally but nobody owns alert triage. No defined thresholds and no measured time to detect.</t>
+          <t>Logging centralised, but no alert ownership and no defined thresholds.</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>No documented incident response plan. The 24-hour OSFI reporting path has never been walked through.</t>
+          <t>No documented incident response plan. OSFI 24-hour reporting path never walked through.</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Backups tested quarterly and RTOs defined for the core banking platform. Wider BCP not exercised this year.</t>
+          <t>Backups tested quarterly. RTOs defined for core banking only; wider BCP not exercised.</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2028-03-04</t>
+          <t>2028-03-05</t>
         </is>
       </c>
       <c r="M2" t="b">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2027-08-07</t>
+          <t>2027-08-08</t>
         </is>
       </c>
       <c r="M3" t="b">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="M4" t="b">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="M5" t="b">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2027-07-03</t>
+          <t>2027-07-04</t>
         </is>
       </c>
       <c r="M6" t="b">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2028-05-23</t>
+          <t>2028-05-24</t>
         </is>
       </c>
       <c r="M7" t="b">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="M8" t="b">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M9" t="b">
